--- a/www/download/COUNTRY.GRC.EXI382.xlsx
+++ b/www/download/COUNTRY.GRC.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Grécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.8956</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.568</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.877</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.925</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>4.072</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.099</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.157</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.238</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.341</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.385</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.424</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.567</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.558</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.489</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.387</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.089</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3.761</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>3.315</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3.301</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>3.133</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>3.264</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>3.277</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>3.343</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3.373</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.056</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.129</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2.332</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.408</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.446</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.533</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.607</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.686</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.817</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.848</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.903</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.971</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.993</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.932</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.825</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.584</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.339</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.204</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2.028</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>1.881</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1.938</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1.931</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>1.953</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1.952</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7662.504</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8616.147</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>8629.81</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>8581.28</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8977.125</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>9123.421</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9179.603</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>9195.814</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>9333.985</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>9588.609</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>9668.449</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>9699.362</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>9800.217</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>9849.725</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>9805.815</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>9587.005</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>9376.645</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8737.796</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8021.353</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>7513.78</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>7130.833</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7123.238</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>6775.317</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7053.37</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>7108.471</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>7258.284</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>7311.421</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4203.683</t>
+          <t>16565341852.0092</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>126.283</t>
+          <t>19797873933.1133</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>184.024</t>
+          <t>17103021444.8707</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>309.592</t>
+          <t>17002429996.462</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>560.613</t>
+          <t>18369809937.347</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>837.343</t>
+          <t>19228802799.3336</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>974.885</t>
+          <t>20170284213.3114</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1344.94</t>
+          <t>20245462403.9369</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1431.205</t>
+          <t>19786343597.2439</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1478.552</t>
+          <t>20072192069.4573</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1963.929</t>
+          <t>18809905654.8416</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025.122</t>
+          <t>19492020129.1828</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5927.617</t>
+          <t>19719170914.6089</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6038.021</t>
+          <t>19585384685.1355</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6072.191</t>
+          <t>16821939810.4021</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2158.263</t>
+          <t>17276392934.6958</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5676.534</t>
+          <t>15805258398.0836</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1647.782</t>
+          <t>15032854567.8345</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1331.109</t>
+          <t>13615293779.3275</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4425.532</t>
+          <t>11681854479.6268</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4110.718</t>
+          <t>10366126624.8212</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4053.618</t>
+          <t>10515807565.2229</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3847.049</t>
+          <t>9921285371.34803</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3963.208</t>
+          <t>10909377500.9206</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>3971.431</t>
+          <t>11140303769.4605</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>4028.577</t>
+          <t>11562028981.4351</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4016.035</t>
+          <t>11165740524.3527</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2872665613.50762</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4152667842.26052</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3426556737.55929</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3429344330.2115</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3106886575.51941</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3936572461.68847</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3604979024.56311</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3998774504.21976</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4029628899.37897</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4384664624.46862</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4154792047.88514</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4148722462.91001</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4067020187.91803</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4277228063.60452</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3926894461.56329</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3494981702.6059</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3018960503.55878</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2657280321.21106</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2593891340.31417</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2181679132.32386</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2066405604.1373</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1987869725.42042</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1905616450.53478</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1970653752.30582</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1928062440.65759</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1798482745.25049</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1995414483.7851</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>27115555.2827904</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>28953466.9926386</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>66488116.706645</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>22809897.0690464</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>21959630.5966115</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>19114537.1843149</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>16560753.8169837</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>17814351.7449357</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>16016497.3634785</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>14607087.3276652</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>13846583.2422782</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>13298334.4620025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>11095263.7821576</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>11646003.173325</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1771599499.92593</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10225456.7752108</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>10829974.0482468</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>8560121.25993185</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8500745.81243964</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>8515104.07321786</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>9413125.62435327</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7561905.32098813</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>8122454.61554046</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7590199.2268097</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>7491503.70396729</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>7467459.05738066</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>6801132.60998191</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13875.5304489022</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>38089.0057548648</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>41618.8819657191</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>41734.5242377587</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>45186.1501518947</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>54489.0677156841</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>54555.0980112347</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>52663.9758755847</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>47998.2109901437</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>48178.2388685103</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>50964.5877466905</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>53945.7236852804</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>55850.450082606</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>56100.8133638857</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>54507.637860339</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>60639.3241895485</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>61669.9648238679</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>61437.7665742136</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>55309.7960354959</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>52148.1717914842</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>52372.6445667747</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>48078.5227059987</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>48362.810998476</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>52478.5919809569</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>56873.005963829</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>55750.304324964</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>56057.4971923022</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>61749.0120455046</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>150445.477970361</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>141555.278085528</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>144672.674051551</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>164874.460461805</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>206302.238475891</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>217289.459152226</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>211416.008903452</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>189806.071826476</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>188165.194678564</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>189035.258970427</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>209545.256993026</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>219630.393304103</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>219190.019326479</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>188660.563161015</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>223441.804764468</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>212806.910860381</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>223408.499937257</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>197652.937261241</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>175534.335481188</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>175956.158590219</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>162694.662351191</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>162283.364173089</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>173551.337736059</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>188826.708856184</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>186431.439366949</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>176761.043688903</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.463338922130909</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.969589910680607</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.946294775165212</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.909722684516741</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.819557944464155</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.787291353544778</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.729572629034647</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.663661954786911</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.644829577179954</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.662790172879293</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.527309916509678</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.511868528660374</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.457484036496269</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.411666834270787</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.546308682199673</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.382468011666542</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.880294224886</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.379899069417749</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.486829313429754</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.0284981741022</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.989308394310535</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.03917674333918</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.01879494392921</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.0111134124913</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.05980390105779</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.23998645301249</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.01263187909229</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1397.18183371574</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1950.98324747897</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1579.13117542729</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1572.73301087482</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1332.28412329374</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1634.44984915468</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1474.06731458992</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1578.48438961727</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1545.57720902873</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1632.23192661581</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1474.95191447437</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1456.50978195187</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1401.11626689592</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1439.65939535603</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1312.24543410634</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1192.1755023211</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1068.65858533094</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1028.39905615985</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1108.73748250245</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>989.669336310848</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1018.69367837124</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>998.984074560645</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1013.03102881124</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1016.66307085556</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>998.529096186377</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>921.015510973891</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1022.48491376969</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-1463652315.31945</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>2531077576.57628</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1018677831.92793</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>619049482.901935</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1298417388.62352</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1781057630.93949</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1914982838.52667</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>1819674097.65765</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1410665184.07551</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2352055011.22169</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2434570733.36396</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>1880012206.25677</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1549732541.93847</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>2193216440.7747</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>1333812491.06912</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>1452711740.57693</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>1397851260.128</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1474510053.10547</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1623568321.75163</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1620404038.9173</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1608531098.67048</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1492346813.78878</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1338461428.55903</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>1151882584.6702</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1105135345.7035</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>1292934785.32269</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>731004430.795922</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-1860267181.70476</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2428208530.15976</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>627449163.475385</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>278118059.693305</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>609771788.513849</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>861839104.703166</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>934865614.252094</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>545464774.091701</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>106319626.379521</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>436853823.7039</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>474500943.965615</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>180657559.228327</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>288206092.678071</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>641329226.33731</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>438636478.497321</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>742164477.123066</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>491639810.03732</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>468804245.986686</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>472245638.587834</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>361141587.764679</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>552034204.750603</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>428285302.849382</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>412348618.234696</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-30402202.2297248</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-99259765.7528648</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-54313441.2709045</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>775665793.408163</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>396614866.385302</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>102869046.416525</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>391228668.452546</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>340931423.20863</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>688645600.109674</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>919218526.236319</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>980117224.274575</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1274209323.56595</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1304345557.69599</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1915201187.5178</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1960069789.39834</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1699354647.02844</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1261526449.2604</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1551887214.43739</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>895176012.5718</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>710547263.453862</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>906211450.090679</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1005705807.11879</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1151322683.1638</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1259262451.15262</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1056496893.91988</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1064061510.93939</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>926112810.324338</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1182284786.89992</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1204395111.45637</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1347248226.5936</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-44661362.6122411</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>2044.55055857048</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>59.3295748164744</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>84.8075948199458</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>141.982114193681</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>240.400085764893</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>347.661615112634</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>398.628148510511</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>530.904354003249</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>548.943310831758</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>550.404645795016</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>697.195143597098</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>710.968262884726</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>2042.10459227605</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>2032.31942107045</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2029.13650793551</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>736.206508390787</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>2009.39256637262</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>637.71121173463</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>568.971575121948</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>2007.54244167149</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>2026.49588561498</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>2037.10509181028</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>2045.10191900752</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>2044.62473778221</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>2056.77412764441</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>2063.06226759589</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>2057.8857333438</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2147.75225021054</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>2222.48942426663</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>2198.73372569978</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>2194.9253120521</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2204.59847740731</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2226.03903867269</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2212.1124418629</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>2212.34037434305</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>2202.65834434629</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2208.74619920719</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2204.69033611481</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>2192.54080202559</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>2172.80440759104</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>2156.52778386029</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>2151.34159719138</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>2135.85639174783</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>2137.22448886636</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2137.05970112795</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2132.60122829858</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>2134.73250851651</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2151.27244114805</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>2157.93064640795</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>2162.23960292672</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>2160.6368410804</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>2168.91135060845</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>2171.47627432463</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2167.81876896971</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12920.3422439168</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>14530.726449865</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>19809.5686540723</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>20241.6451328192</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>27805.1600862109</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>36792.2023787026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>37337.7932610695</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>34573.7313541689</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>33047.419875568</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>39711.4962984021</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>42316.4201506108</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>45234.5753776308</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>51128.890062848</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>53174.9004915858</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>42968.7428338106</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>50739.8477285886</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>57472.3530118598</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>62084.6354958569</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>62309.3355045196</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>66109.6800275931</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>65925.902203203</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>62813.2111684842</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>71756.4536235334</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>81372.8849902626</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>85953.6802617831</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>90118.816567981</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>90889.6508309388</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>970496871.282684</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1719482644.27832</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1874055587.44751</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1971288921.92483</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2514262503.54032</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2995474133.2768</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2834018447.0285</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2594534713.47841</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2288222856.2652</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2615019769.69525</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2550377815.34674</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2883101486.70409</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2940778285.47009</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3089051148.90929</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2785538242.03237</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3049362258.93348</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3229431091.4804</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>3470558572.81379</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3468877539.51081</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>3201186205.39242</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2782432860.44463</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2772881080.74612</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2886951635.61651</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>3607382488.10471</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>3811802185.85595</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>4047928210.60722</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3752910299.10239</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>24223.4621276697</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>27937.2142421045</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>31086.3967109001</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>36544.9755906235</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>44033.2789627216</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>57272.317151133</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>58346.7861725546</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>56115.696454395</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>58965.2016486562</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>61165.2736634007</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>63876.7205000318</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>75135.3996976139</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>89074.4571380102</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>92915.6106893002</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>73230.8647645653</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>73001.2997734755</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>73019.9593168276</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>73360.8410430041</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>68100.7834432052</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>69710.0646877782</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>68285.7974024821</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>66107.3964331392</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>75252.1418297789</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>86359.6576080839</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>89929.7908217512</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>94830.9213499591</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>96410.8191811909</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7662.504</t>
+          <t>5910358560.56588</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8616.147</t>
+          <t>6973927992.45783</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8629.81</t>
+          <t>5003617120.43914</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8581.28</t>
+          <t>5661858482.06573</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8977.125</t>
+          <t>6789629192.60533</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9123.421</t>
+          <t>7953828615.3199</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9179.603</t>
+          <t>8137310412.94461</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9195.814</t>
+          <t>8018902321.44764</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9333.985</t>
+          <t>8101740085.01352</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9588.609</t>
+          <t>8901479614.67157</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9668.449</t>
+          <t>8590921380.19529</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9699.362</t>
+          <t>9212108162.79569</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>9800.217</t>
+          <t>9202682568.63041</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9849.725</t>
+          <t>10728308661.7467</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9805.815</t>
+          <t>8573675129.20781</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>9587.005</t>
+          <t>7246955924.29738</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>9376.645</t>
+          <t>6420166315.88132</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8737.796</t>
+          <t>6174527203.87874</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8021.353</t>
+          <t>5755876821.70764</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7513.78</t>
+          <t>5204333069.18055</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>7130.833</t>
+          <t>4619082953.39488</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>7123.238</t>
+          <t>4614597758.61656</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>6775.317</t>
+          <t>4562127389.89412</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7053.37</t>
+          <t>5254898937.92147</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>7108.471</t>
+          <t>5279826828.72491</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>7258.284</t>
+          <t>5798131894.23685</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>7311.421</t>
+          <t>5021870176.59387</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4203.683</t>
+          <t>-11303.1198837529</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>126.283</t>
+          <t>-13406.4877922395</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>184.024</t>
+          <t>-11276.8280568279</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>309.592</t>
+          <t>-16303.3304578044</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>560.613</t>
+          <t>-16228.1188765107</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>837.343</t>
+          <t>-20480.1147724303</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>974.885</t>
+          <t>-21008.9929114851</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1344.94</t>
+          <t>-21541.9651002261</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1431.205</t>
+          <t>-25917.7817730882</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1478.552</t>
+          <t>-21453.7773649986</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1963.929</t>
+          <t>-21560.300349421</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2025.122</t>
+          <t>-29900.8243199831</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5927.617</t>
+          <t>-37945.5670751623</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6038.021</t>
+          <t>-39740.7101977144</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6072.191</t>
+          <t>-30262.1219307547</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2158.263</t>
+          <t>-22261.4520448868</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5676.534</t>
+          <t>-15547.6063049678</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1647.782</t>
+          <t>-11276.2055471472</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1331.109</t>
+          <t>-5791.44793868557</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>4425.532</t>
+          <t>-3600.38466018508</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>4110.718</t>
+          <t>-2359.89519927915</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>4053.618</t>
+          <t>-3294.18526465498</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>3847.049</t>
+          <t>-3495.68820624556</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3963.208</t>
+          <t>-4986.77261782129</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>3971.431</t>
+          <t>-3976.11055996804</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>4028.577</t>
+          <t>-4712.10478197809</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>4016.035</t>
+          <t>-5521.16835025216</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8082.07</t>
+          <t>-4939861689.2832</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10273.513</t>
+          <t>-5254445348.17951</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9177.289</t>
+          <t>-3129561532.99164</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9193.266</t>
+          <t>-3690569560.1409</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9818.265</t>
+          <t>-4275366689.06501</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10257.811</t>
+          <t>-4958354482.04309</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10636.215</t>
+          <t>-5303291965.91611</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10645.582</t>
+          <t>-5424367607.96923</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10475.295</t>
+          <t>-5813517228.74832</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10706.12</t>
+          <t>-6286459844.97632</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10122.926</t>
+          <t>-6040543564.84855</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10513.113</t>
+          <t>-6329006676.0916</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10722.121</t>
+          <t>-6261904283.16033</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10657.322</t>
+          <t>-7639257512.83744</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9282.084</t>
+          <t>-5788136887.17544</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>9498.93</t>
+          <t>-4197593665.3639</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>8759.345</t>
+          <t>-3190735224.40092</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>8339.01</t>
+          <t>-2703968631.06495</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>7491.323</t>
+          <t>-2286999282.19683</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6535.836</t>
+          <t>-2003146863.78813</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>5758.386</t>
+          <t>-1836650092.95025</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>5828.647</t>
+          <t>-1841716677.87044</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>5597.415</t>
+          <t>-1675175754.27761</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6212.154</t>
+          <t>-1647516449.81676</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>6331.976</t>
+          <t>-1468024642.86896</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>6556.062</t>
+          <t>-1750203683.62963</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>6349.518</t>
+          <t>-1268959877.49147</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>20972.0259639925</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>23397.4416494054</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>25325.7264692064</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>26407.396812658</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>27768.3601750497</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>29104.2804703913</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>31002.9086340104</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>37483.184774724</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>38782.3291680346</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>41762.3214805871</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>40935.589154016</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>46783.2362703499</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>48635.022306976</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>49465.9812081324</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>48954.8743691558</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>45158.1873872449</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>39576.4594760886</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>44060.2489850968</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>41413.7612728377</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>34676.8010648922</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>32964.4970016122</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>31921.651353184</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>37308.2660298803</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>38330.1983798672</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>38644.6461364094</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>39346.1613794021</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>40015.4828246474</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3722.374</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>5012.323</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>5028.485</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>4904.785</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>5034.503</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>5078.76</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5064.175</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>5043.168</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>5003.576</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>5139.329</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>5071.218</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>5018.062</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>5014.445</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>5012.801</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4860.18</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>4688.598</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>4580.254</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>4134.064</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>3810.007</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>3470.474</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>3085.436</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3107.567</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2956.688</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>3298.786</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>3355.365</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>3457.5</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3541.071</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>32789.5464067325</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>39609.1800922822</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>42547.0769904714</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>43332.3557603831</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>45293.4675051833</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>50137.5482177656</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>49923.3267877192</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>57393.3056608165</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>61812.5336645465</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>67593.131484678</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>69526.5562370285</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>75632.4063306604</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>82093.5821113811</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>86817.507643315</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>85985.95954308</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>85622.1404446432</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>73033.4943346942</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>67483.8826949643</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>66940.4766673623</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>65053.2534881922</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>62925.4855510833</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>60777.8633000031</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>64050.8166741695</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>63798.2548048081</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>64742.317790655</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>58469.8180056114</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>67479.5683093736</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2476.565</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3655.6</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3058.751</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3087.762</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2781.529</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3540.139</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3258.784</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>3628.53</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>3763.262</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>4017.63</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>3976.662</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>3964.053</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>3804.511</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>4106.459</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>3844.927</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>3184.482</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2813.494</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2441.286</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2438.23</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2069.099</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1976.432</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1896.421</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>1846.431</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>1934.412</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1904.387</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>1797.151</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1962.165</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>69.74</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-96.55</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-93.98</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-89.97</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-79.85</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-76.35</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-70.08</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-62.93</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-61.97</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-63.2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-50.61</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-48.91</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>47.04</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>57.93</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-32.23</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>101.76</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-32.5</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-45.41</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>113.89</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>107.99</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>113.75</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>108.35</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>104.88</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>108.54</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>124.16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>104.67</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>19.976</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>20.769</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>55.544</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>16.484</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>15.342</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>13.555</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>11.753</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>12.638</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>11.036</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>10.324</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>9.729</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>9.643</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>7.966</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>8.391</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1584.761</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>7.568</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>8.056</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>6.216</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>6.125</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>6.328</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>7.251</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>5.622</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>6.289</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>5.715</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>5.643</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>5.613</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>5.129</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>55400.1886444629</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>57258.7530674446</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>64705.740170045</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>66463.5165800138</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>74380.1474991927</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>71216.9436174911</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>78513.8587903853</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>79894.4074299994</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>90678.1355539771</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>98056.1392555627</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>101611.722971328</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>110004.466896662</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>115917.28033347</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>119817.300615167</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>117496.119653485</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>108603.985438284</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>101824.934441928</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>94598.5375771944</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>87515.6347419557</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>87478.8110326649</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>88686.6243824202</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>89124.2290535748</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>87998.6274646682</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>90790.58352105</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>92838.9088768421</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>102696.213396951</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>96498.2767946807</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4203683402.51277</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>126282999.996913</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>184023999.99978</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>309591999.999228</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>560613000.003446</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>837342999.998655</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>974884999.997845</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1344939999.99721</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1431205000.0003</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1478551999.99934</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1963928999.99975</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2025122000.00002</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5927616999.99859</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6038021000.00276</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6072190999.99713</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2158262999.99928</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5676534000.0005</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1647782000.00088</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1331108999.99764</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>4425532136.39581</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>4110718014.36065</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>4053617712.86537</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3847048855.40794</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>3963208192.63853</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>3971430536.74952</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>4028576985.33781</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>4016034802.06838</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7662504185.98153</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8616146999.99837</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>8629810000.00012</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8581279999.9982</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8977125000.0017</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9123421000.00045</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9179602999.99891</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9195813999.99754</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9333985000.00123</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9588608999.99924</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9668449000.00069</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9699361999.99989</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>9800216999.99885</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>9849725000.0039</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9805814999.99804</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>9587005000.00074</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>9376645000.00135</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8737796000.00036</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8021352999.99865</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>7513779761.8819</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>7130833315.91656</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>7123237969.22613</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>6775317391.62617</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>7053369542.70599</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>7108470579.69951</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>7258284321.42807</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>7311421357.19344</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3722373810.52577</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5012323031.21134</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5028485270.19358</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4904784759.38926</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5034503147.21741</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5078759908.59338</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5064174932.66788</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5043168439.14074</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5003575942.35569</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5139329118.69752</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5071218419.64474</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5018062193.56142</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5014445197.08085</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5012801286.55911</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4860179509.32998</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4688597968.93137</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4580254116.28406</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4134063879.13666</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3810007239.62241</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3470474039.03485</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>3085435994.99858</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3107566563.58606</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2956687838.71574</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>3298786273.30275</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>3355365173.48269</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>3457499639.10505</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3541071352.77777</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3567685.32554459</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3876800.00000067</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3924900.00000048</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3909599.99999969</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4071999.99999961</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4098500.0000002</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4149700.00000019</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4156600.00000145</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4237599.99999973</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4341200.00000044</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4385400.00000127</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4423799.99999958</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4510400.00000011</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4567400.00000018</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4557999.99999988</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4488600.00000067</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4387299.99999905</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4088699.99999931</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3761299.99999963</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>3519775.77139323</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>3314704.90651156</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>3300957.78614726</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>3133472.06408364</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>3264486.38132961</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>3277437.12425377</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>3342557.50672917</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3372708.76230504</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2056042.77423784</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2128500.00000079</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2169899.99999976</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2180499.99999934</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2331999.99999881</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2408499.99999965</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2445600.00000135</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2533300.00000147</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2607199.99999953</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2686300.00000035</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2816900.00000156</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2848399.99999882</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2902699.99999947</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2971000.00000121</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2992500.00000006</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2931600.00000115</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2824999.99999893</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2583899.99999964</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2339499.99999972</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2204452.59065661</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2028485.74405725</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>1989891.30662037</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1881103.73358551</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>1938354.80878384</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1930902.61267431</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>1952717.10825886</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1951534.40105872</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7662504185.98153</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8616146999.99837</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8629810000.00012</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8581279999.9982</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8977125000.0017</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9123421000.00045</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9179602999.99891</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9195813999.99754</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9333985000.00123</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9588608999.99924</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9668449000.00069</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9699361999.99989</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>9800216999.99885</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>9849725000.0039</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>9805814999.99804</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>9587005000.00074</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>9376645000.00135</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8737796000.00036</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8021352999.99865</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>7513779761.8819</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>7130833315.91656</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>7123237969.22613</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>6775317391.62617</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>7053369542.70599</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>7108470579.69951</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>7258284321.42807</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>7311421357.19344</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4203683402.51277</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>126282999.996913</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>184023999.99978</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>309591999.999228</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>560613000.003446</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>837342999.998655</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>974884999.997845</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1344939999.99721</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1431205000.0003</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1478551999.99934</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1963928999.99975</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2025122000.00002</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5927616999.99859</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6038021000.00276</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6072190999.99713</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2158262999.99928</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5676534000.0005</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1647782000.00088</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1331108999.99764</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>4425532136.39581</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>4110718014.36065</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>4053617712.86537</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>3847048855.40794</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>3963208192.63853</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>3971430536.74952</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>4028576985.33781</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>4016034802.06838</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>146919.000424263</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>160543.287720476</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>172506.789456123</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>179577.512478247</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>193165.109974941</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>203890.272149812</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>215888.326198619</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>226542.677932053</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>247227.599613398</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>263131.806550565</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>271211.290813374</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>301320.878099086</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>320064.468149531</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>330023.857800945</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>313696.718657107</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>325549.225621772</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>294542.85235708</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>291009.076511744</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>276365.188732283</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>265928.213683709</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>264279.911108152</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>260619.745566363</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>272274.265324191</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>278210.84009187</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>285107.904192593</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>289870.149839984</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>301964.752772851</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>38327.0621713343</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>45624.2460690881</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>48349.7806323788</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>48915.438556528</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>50955.377307199</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>56509.045434385</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>57676.2759734772</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>65809.1279687802</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>69184.1825538888</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>75125.1476527608</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>76757.3285795363</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>84938.8481195993</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>92205.3843781715</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>96029.0785367632</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>94384.0233582427</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>91928.3654514744</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>80013.7874332555</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>74130.5597386659</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>73305.323922189</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>71144.1698642243</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>68976.1152932261</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>66816.8801942598</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>70655.9571287731</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>70166.9871922584</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>71422.4788395626</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>65211.7771268116</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>74275.9031271737</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
